--- a/cl_st1_ph3_ednalvo/corpus/00_fontes/composicoes_de_admissao_universitaria.xlsx
+++ b/cl_st1_ph3_ednalvo/corpus/00_fontes/composicoes_de_admissao_universitaria.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>caminho_em_composicoes_brutas</t>
+          <t>caminho_em_composicoes</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36237.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36237.txt</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/46656.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/46656.txt</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -582,7 +582,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36560.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36560.txt</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36923.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36923.txt</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/45355.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/45355.txt</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35994.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35994.txt</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40127.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40127.txt</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40621.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40621.txt</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34726.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34726.txt</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34811.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34811.txt</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36280.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36280.txt</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37681.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37681.txt</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39896.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39896.txt</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38047.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38047.txt</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39608.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39608.txt</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40140.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40140.txt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35240.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35240.txt</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36415.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36415.txt</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33890.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33890.txt</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34096.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34096.txt</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34148.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34148.txt</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34813.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34813.txt</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34844.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34844.txt</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36030.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36030.txt</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37293.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37293.txt</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38333.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38333.txt</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39561.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39561.txt</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36349.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36349.txt</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36441.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36441.txt</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37321.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37321.txt</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38105.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38105.txt</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40134.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40134.txt</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40676.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40676.txt</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/46260.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/46260.txt</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/46711.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/46711.txt</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35400.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35400.txt</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35733.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35733.txt</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35819.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35819.txt</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36403.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36403.txt</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37193.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37193.txt</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37525.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37525.txt</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37605.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37605.txt</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37924.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37924.txt</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38475.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38475.txt</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40021.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40021.txt</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40548.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40548.txt</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40772.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40772.txt</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34306.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34306.txt</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34841.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34841.txt</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35134.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35134.txt</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36074.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36074.txt</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36163.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36163.txt</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36551.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36551.txt</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36566.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36566.txt</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36650.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36650.txt</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39585.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39585.txt</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40286.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40286.txt</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40713.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40713.txt</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34277.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34277.txt</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34717.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34717.txt</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34754.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34754.txt</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34901.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34901.txt</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35789.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35789.txt</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36090.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36090.txt</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38958.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38958.txt</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39465.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39465.txt</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39509.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39509.txt</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39989.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39989.txt</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40024.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40024.txt</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40429.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40429.txt</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/45141.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/45141.txt</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/46003.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/46003.txt</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/46597.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/46597.txt</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33927.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33927.txt</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34084.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34084.txt</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34641.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34641.txt</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34698.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34698.txt</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35100.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35100.txt</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35247.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35247.txt</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35497.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35497.txt</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36471.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36471.txt</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36926.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36926.txt</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37612.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37612.txt</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37961.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37961.txt</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38742.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38742.txt</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39305.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39305.txt</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40060.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40060.txt</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40173.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40173.txt</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40580.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40580.txt</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33895.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33895.txt</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33991.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33991.txt</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34648.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34648.txt</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35763.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35763.txt</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35892.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35892.txt</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35934.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35934.txt</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36330.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36330.txt</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36436.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36436.txt</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36515.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36515.txt</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36822.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36822.txt</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37102.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37102.txt</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37376.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37376.txt</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37687.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37687.txt</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38392.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38392.txt</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38437.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38437.txt</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39650.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39650.txt</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39715.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39715.txt</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40297.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40297.txt</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40615.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40615.txt</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40943.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40943.txt</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33879.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33879.txt</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34281.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34281.txt</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34652.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34652.txt</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34994.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34994.txt</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35053.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35053.txt</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35121.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35121.txt</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35865.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35865.txt</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36068.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36068.txt</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36503.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36503.txt</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36532.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36532.txt</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36937.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36937.txt</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37015.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37015.txt</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37126.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37126.txt</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37362.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37362.txt</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37480.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37480.txt</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37662.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37662.txt</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38406.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38406.txt</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38641.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38641.txt</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38845.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38845.txt</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38848.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38848.txt</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40013.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40013.txt</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40975.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40975.txt</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/45059.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/45059.txt</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/45169.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/45169.txt</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/45279.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/45279.txt</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/46321.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/46321.txt</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33669.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33669.txt</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33999.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33999.txt</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34353.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34353.txt</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35077.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35077.txt</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35464.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35464.txt</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35750.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35750.txt</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35928.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35928.txt</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36006.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36006.txt</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36064.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36064.txt</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36691.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36691.txt</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36707.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36707.txt</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36743.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36743.txt</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36782.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36782.txt</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36845.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36845.txt</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36945.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36945.txt</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37655.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37655.txt</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38020.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38020.txt</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38080.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38080.txt</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38236.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38236.txt</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38784.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38784.txt</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39131.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39131.txt</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39635.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39635.txt</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39684.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39684.txt</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39810.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39810.txt</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40004.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40004.txt</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40130.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40130.txt</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40449.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40449.txt</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40697.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40697.txt</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/41088.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/41088.txt</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/45576.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/45576.txt</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/46771.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/46771.txt</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/32875.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/32875.txt</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33083.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33083.txt</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33228.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33228.txt</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33849.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33849.txt</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34032.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34032.txt</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34116.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34116.txt</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34419.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34419.txt</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34511.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34511.txt</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34675.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34675.txt</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34802.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34802.txt</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35125.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35125.txt</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35451.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35451.txt</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35496.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35496.txt</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35647.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35647.txt</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35867.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35867.txt</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36214.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36214.txt</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36260.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36260.txt</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36261.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36261.txt</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36494.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36494.txt</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36626.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36626.txt</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36777.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36777.txt</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36862.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36862.txt</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36988.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36988.txt</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37284.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37284.txt</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37386.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37386.txt</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37753.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37753.txt</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37801.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37801.txt</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37817.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37817.txt</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37922.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37922.txt</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38367.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38367.txt</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38562.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38562.txt</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38612.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38612.txt</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38672.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38672.txt</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39108.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39108.txt</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39227.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39227.txt</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39663.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39663.txt</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40289.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40289.txt</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40710.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40710.txt</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/41022.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/41022.txt</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/45015.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/45015.txt</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/45081.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/45081.txt</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/45186.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/45186.txt</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/32757.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/32757.txt</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33914.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33914.txt</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34175.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34175.txt</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34381.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34381.txt</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34461.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34461.txt</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34832.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34832.txt</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34875.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34875.txt</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34967.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34967.txt</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35126.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35126.txt</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35378.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35378.txt</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35482.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35482.txt</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35542.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35542.txt</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/35734.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/35734.txt</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36245.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36245.txt</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36385.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36385.txt</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36442.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36442.txt</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36577.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36577.txt</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36769.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36769.txt</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36794.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36794.txt</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36966.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36966.txt</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/36976.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/36976.txt</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37416.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37416.txt</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37754.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37754.txt</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/37783.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/37783.txt</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38061.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38061.txt</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38493.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38493.txt</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/38584.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/38584.txt</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39244.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39244.txt</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39298.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39298.txt</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39614.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39614.txt</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/39716.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/39716.txt</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/40663.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/40663.txt</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/41023.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/41023.txt</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/46479.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/46479.txt</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/46998.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/46998.txt</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -11112,7 +11112,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/47002.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/47002.txt</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/47099.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/47099.txt</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -11196,7 +11196,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33383.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33383.txt</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -11242,7 +11242,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33975.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33975.txt</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/33978.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/33978.txt</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34050.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34050.txt</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/maiores_notas/34086.txt</t>
+          <t>corpus/01_composicoes/maiores_notas/34086.txt</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34356.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34356.txt</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35071.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35071.txt</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35217.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35217.txt</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37999.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37999.txt</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38172.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38172.txt</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38677.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38677.txt</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39124.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39124.txt</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -11732,7 +11732,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40426.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40426.txt</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46743.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46743.txt</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40929.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40929.txt</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37224.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37224.txt</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45075.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45075.txt</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34362.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34362.txt</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/47046.txt</t>
+          <t>corpus/01_composicoes/menores_notas/47046.txt</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38310.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38310.txt</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39164.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39164.txt</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/32674.txt</t>
+          <t>corpus/01_composicoes/menores_notas/32674.txt</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -12176,7 +12176,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38555.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38555.txt</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46273.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46273.txt</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/32792.txt</t>
+          <t>corpus/01_composicoes/menores_notas/32792.txt</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35549.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35549.txt</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35577.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35577.txt</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36742.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36742.txt</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38196.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38196.txt</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38794.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38794.txt</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38928.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38928.txt</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38957.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38957.txt</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40496.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40496.txt</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/32755.txt</t>
+          <t>corpus/01_composicoes/menores_notas/32755.txt</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36000.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36000.txt</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37010.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37010.txt</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37345.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37345.txt</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/32782.txt</t>
+          <t>corpus/01_composicoes/menores_notas/32782.txt</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -12876,7 +12876,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34025.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34025.txt</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34714.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34714.txt</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35291.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35291.txt</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36181.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36181.txt</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36238.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36238.txt</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36524.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36524.txt</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37078.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37078.txt</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38917.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38917.txt</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39446.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39446.txt</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39914.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39914.txt</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40368.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40368.txt</t>
         </is>
       </c>
       <c r="E295" t="inlineStr"/>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40887.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40887.txt</t>
         </is>
       </c>
       <c r="E296" t="inlineStr"/>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/41093.txt</t>
+          <t>corpus/01_composicoes/menores_notas/41093.txt</t>
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45268.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45268.txt</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -13488,7 +13488,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45638.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45638.txt</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45746.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45746.txt</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -13576,7 +13576,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33167.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33167.txt</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33436.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33436.txt</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33497.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33497.txt</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33645.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33645.txt</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34236.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34236.txt</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34895.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34895.txt</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35131.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35131.txt</t>
         </is>
       </c>
       <c r="E307" t="inlineStr"/>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35220.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35220.txt</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35906.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35906.txt</t>
         </is>
       </c>
       <c r="E309" t="inlineStr"/>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36172.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36172.txt</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36188.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36188.txt</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36248.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36248.txt</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -14116,7 +14116,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36616.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36616.txt</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37212.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37212.txt</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38036.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38036.txt</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39516.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39516.txt</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/41096.txt</t>
+          <t>corpus/01_composicoes/menores_notas/41096.txt</t>
         </is>
       </c>
       <c r="E317" t="inlineStr"/>
@@ -14334,7 +14334,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46699.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46699.txt</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/32714.txt</t>
+          <t>corpus/01_composicoes/menores_notas/32714.txt</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -14426,7 +14426,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33787.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33787.txt</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34807.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34807.txt</t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35173.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35173.txt</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35228.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35228.txt</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35457.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35457.txt</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35911.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35911.txt</t>
         </is>
       </c>
       <c r="E325" t="inlineStr"/>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36095.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36095.txt</t>
         </is>
       </c>
       <c r="E326" t="inlineStr"/>
@@ -14736,7 +14736,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36522.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36522.txt</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37034.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37034.txt</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37377.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37377.txt</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38158.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38158.txt</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38499.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38499.txt</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38764.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38764.txt</t>
         </is>
       </c>
       <c r="E332" t="inlineStr"/>
@@ -15008,7 +15008,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38970.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38970.txt</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40270.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40270.txt</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40865.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40865.txt</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45044.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45044.txt</t>
         </is>
       </c>
       <c r="E336" t="inlineStr"/>
@@ -15188,7 +15188,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45389.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45389.txt</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46034.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46034.txt</t>
         </is>
       </c>
       <c r="E338" t="inlineStr"/>
@@ -15272,7 +15272,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33465.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33465.txt</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -15318,7 +15318,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33789.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33789.txt</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34642.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34642.txt</t>
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
@@ -15406,7 +15406,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34743.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34743.txt</t>
         </is>
       </c>
       <c r="E342" t="inlineStr"/>
@@ -15448,7 +15448,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35056.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35056.txt</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36137.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36137.txt</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36727.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36727.txt</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37043.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37043.txt</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37664.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37664.txt</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38445.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38445.txt</t>
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
@@ -15720,7 +15720,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38451.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38451.txt</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -15766,7 +15766,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38506.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38506.txt</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38632.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38632.txt</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
@@ -15850,7 +15850,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38786.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38786.txt</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -15896,7 +15896,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39065.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39065.txt</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39379.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39379.txt</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -15988,7 +15988,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39727.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39727.txt</t>
         </is>
       </c>
       <c r="E355" t="inlineStr"/>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39833.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39833.txt</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39956.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39956.txt</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40688.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40688.txt</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/41011.txt</t>
+          <t>corpus/01_composicoes/menores_notas/41011.txt</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45124.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45124.txt</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46288.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46288.txt</t>
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46946.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46946.txt</t>
         </is>
       </c>
       <c r="E362" t="inlineStr"/>
@@ -16336,7 +16336,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33871.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33871.txt</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34009.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34009.txt</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -16428,7 +16428,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34046.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34046.txt</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34185.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34185.txt</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34273.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34273.txt</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -16566,7 +16566,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34616.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34616.txt</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34618.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34618.txt</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34638.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34638.txt</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35028.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35028.txt</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35278.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35278.txt</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35852.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35852.txt</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36578.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36578.txt</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36721.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36721.txt</t>
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36797.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36797.txt</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -16972,7 +16972,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36867.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36867.txt</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
@@ -17014,7 +17014,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36872.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36872.txt</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36973.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36973.txt</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
@@ -17102,7 +17102,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37063.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37063.txt</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37158.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37158.txt</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -17194,7 +17194,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37442.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37442.txt</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37489.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37489.txt</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -17282,7 +17282,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38204.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38204.txt</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38284.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38284.txt</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -17370,7 +17370,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38439.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38439.txt</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39436.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39436.txt</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39493.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39493.txt</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -17496,7 +17496,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39722.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39722.txt</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -17538,7 +17538,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39786.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39786.txt</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -17580,7 +17580,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39912.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39912.txt</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39985.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39985.txt</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
@@ -17664,7 +17664,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40256.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40256.txt</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40362.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40362.txt</t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
@@ -17748,7 +17748,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40523.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40523.txt</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40690.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40690.txt</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
@@ -17836,7 +17836,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40765.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40765.txt</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -17882,7 +17882,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40803.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40803.txt</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46249.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46249.txt</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46255.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46255.txt</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
@@ -18016,7 +18016,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46626.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46626.txt</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
@@ -18058,7 +18058,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46724.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46724.txt</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
@@ -18100,7 +18100,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/47010.txt</t>
+          <t>corpus/01_composicoes/menores_notas/47010.txt</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
@@ -18142,7 +18142,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/47068.txt</t>
+          <t>corpus/01_composicoes/menores_notas/47068.txt</t>
         </is>
       </c>
       <c r="E404" t="inlineStr"/>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/32860.txt</t>
+          <t>corpus/01_composicoes/menores_notas/32860.txt</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -18230,7 +18230,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33310.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33310.txt</t>
         </is>
       </c>
       <c r="E406" t="inlineStr"/>
@@ -18272,7 +18272,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33360.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33360.txt</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -18318,7 +18318,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33856.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33856.txt</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34308.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34308.txt</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -18410,7 +18410,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35198.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35198.txt</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35485.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35485.txt</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35633.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35633.txt</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35820.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35820.txt</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35937.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35937.txt</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
@@ -18632,7 +18632,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36079.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36079.txt</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36085.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36085.txt</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36307.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36307.txt</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -18770,7 +18770,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36430.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36430.txt</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -18816,7 +18816,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36547.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36547.txt</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36590.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36590.txt</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36704.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36704.txt</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36827.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36827.txt</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37099.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37099.txt</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37602.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37602.txt</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37858.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37858.txt</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38340.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38340.txt</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38395.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38395.txt</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -19230,7 +19230,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38536.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38536.txt</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38637.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38637.txt</t>
         </is>
       </c>
       <c r="E429" t="inlineStr"/>
@@ -19318,7 +19318,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38670.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38670.txt</t>
         </is>
       </c>
       <c r="E430" t="inlineStr"/>
@@ -19360,7 +19360,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38674.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38674.txt</t>
         </is>
       </c>
       <c r="E431" t="inlineStr"/>
@@ -19402,7 +19402,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39063.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39063.txt</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
@@ -19444,7 +19444,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39302.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39302.txt</t>
         </is>
       </c>
       <c r="E433" t="inlineStr"/>
@@ -19486,7 +19486,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39502.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39502.txt</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39648.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39648.txt</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -19570,7 +19570,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39695.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39695.txt</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -19612,7 +19612,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40617.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40617.txt</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
@@ -19654,7 +19654,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40869.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40869.txt</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40906.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40906.txt</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40926.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40926.txt</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40978.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40978.txt</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45357.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45357.txt</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -19864,7 +19864,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46705.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46705.txt</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/32733.txt</t>
+          <t>corpus/01_composicoes/menores_notas/32733.txt</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
@@ -19948,7 +19948,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33948.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33948.txt</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -19994,7 +19994,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33964.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33964.txt</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -20040,7 +20040,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34210.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34210.txt</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -20086,7 +20086,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34537.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34537.txt</t>
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34637.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34637.txt</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34823.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34823.txt</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35019.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35019.txt</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35214.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35214.txt</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35465.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35465.txt</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -20354,7 +20354,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35661.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35661.txt</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35979.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35979.txt</t>
         </is>
       </c>
       <c r="E455" t="inlineStr"/>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35986.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35986.txt</t>
         </is>
       </c>
       <c r="E456" t="inlineStr"/>
@@ -20484,7 +20484,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36140.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36140.txt</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -20530,7 +20530,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36225.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36225.txt</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -20576,7 +20576,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36278.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36278.txt</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36295.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36295.txt</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -20668,7 +20668,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36341.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36341.txt</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -20714,7 +20714,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/36856.txt</t>
+          <t>corpus/01_composicoes/menores_notas/36856.txt</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -20760,7 +20760,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37094.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37094.txt</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37260.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37260.txt</t>
         </is>
       </c>
       <c r="E464" t="inlineStr"/>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37677.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37677.txt</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -20890,7 +20890,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37694.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37694.txt</t>
         </is>
       </c>
       <c r="E466" t="inlineStr"/>
@@ -20932,7 +20932,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37734.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37734.txt</t>
         </is>
       </c>
       <c r="E467" t="inlineStr"/>
@@ -20974,7 +20974,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37949.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37949.txt</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -21020,7 +21020,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/37994.txt</t>
+          <t>corpus/01_composicoes/menores_notas/37994.txt</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -21066,7 +21066,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38002.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38002.txt</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -21112,7 +21112,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38193.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38193.txt</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -21158,7 +21158,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38226.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38226.txt</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -21204,7 +21204,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38469.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38469.txt</t>
         </is>
       </c>
       <c r="E473" t="inlineStr"/>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38495.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38495.txt</t>
         </is>
       </c>
       <c r="E474" t="inlineStr"/>
@@ -21288,7 +21288,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/38891.txt</t>
+          <t>corpus/01_composicoes/menores_notas/38891.txt</t>
         </is>
       </c>
       <c r="E475" t="inlineStr"/>
@@ -21330,7 +21330,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39349.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39349.txt</t>
         </is>
       </c>
       <c r="E476" t="inlineStr"/>
@@ -21372,7 +21372,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39615.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39615.txt</t>
         </is>
       </c>
       <c r="E477" t="inlineStr"/>
@@ -21414,7 +21414,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/39701.txt</t>
+          <t>corpus/01_composicoes/menores_notas/39701.txt</t>
         </is>
       </c>
       <c r="E478" t="inlineStr"/>
@@ -21456,7 +21456,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40126.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40126.txt</t>
         </is>
       </c>
       <c r="E479" t="inlineStr"/>
@@ -21498,7 +21498,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40461.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40461.txt</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -21544,7 +21544,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/40898.txt</t>
+          <t>corpus/01_composicoes/menores_notas/40898.txt</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45078.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45078.txt</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -21636,7 +21636,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45241.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45241.txt</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45519.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45519.txt</t>
         </is>
       </c>
       <c r="E484" t="inlineStr"/>
@@ -21724,7 +21724,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45531.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45531.txt</t>
         </is>
       </c>
       <c r="E485" t="inlineStr"/>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45667.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45667.txt</t>
         </is>
       </c>
       <c r="E486" t="inlineStr"/>
@@ -21808,7 +21808,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/45996.txt</t>
+          <t>corpus/01_composicoes/menores_notas/45996.txt</t>
         </is>
       </c>
       <c r="E487" t="inlineStr"/>
@@ -21850,7 +21850,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46108.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46108.txt</t>
         </is>
       </c>
       <c r="E488" t="inlineStr"/>
@@ -21892,7 +21892,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46276.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46276.txt</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -21938,7 +21938,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46290.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46290.txt</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -21984,7 +21984,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/46687.txt</t>
+          <t>corpus/01_composicoes/menores_notas/46687.txt</t>
         </is>
       </c>
       <c r="E491" t="inlineStr"/>
@@ -22026,7 +22026,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/47123.txt</t>
+          <t>corpus/01_composicoes/menores_notas/47123.txt</t>
         </is>
       </c>
       <c r="E492" t="inlineStr"/>
@@ -22068,7 +22068,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/32610.txt</t>
+          <t>corpus/01_composicoes/menores_notas/32610.txt</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/32749.txt</t>
+          <t>corpus/01_composicoes/menores_notas/32749.txt</t>
         </is>
       </c>
       <c r="E494" t="inlineStr"/>
@@ -22156,7 +22156,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/33862.txt</t>
+          <t>corpus/01_composicoes/menores_notas/33862.txt</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -22202,7 +22202,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34251.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34251.txt</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -22248,7 +22248,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34613.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34613.txt</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/34971.txt</t>
+          <t>corpus/01_composicoes/menores_notas/34971.txt</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -22340,7 +22340,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35072.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35072.txt</t>
         </is>
       </c>
       <c r="E499" t="inlineStr"/>
@@ -22382,7 +22382,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35136.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35136.txt</t>
         </is>
       </c>
       <c r="E500" t="inlineStr"/>
@@ -22424,7 +22424,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>corpus/01_composicoes_brutas/menores_notas/35163.txt</t>
+          <t>corpus/01_composicoes/menores_notas/35163.txt</t>
         </is>
       </c>
       <c r="E501" t="inlineStr"/>
